--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:40:21+00:00</t>
+    <t>2026-08-31T20:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:52:19+00:00</t>
+    <t>2026-08-31T21:01:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:01:41+00:00</t>
+    <t>2026-08-31T21:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:14:06+00:00</t>
+    <t>2026-08-31T21:19:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:19:30+00:00</t>
+    <t>2026-08-31T21:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:24:22+00:00</t>
+    <t>2026-08-31T21:32:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:32:17+00:00</t>
+    <t>2026-08-31T21:46:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:46:42+00:00</t>
+    <t>2026-08-31T21:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
